--- a/Data/EXCEL/Transfer/salemon/202208/8446-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8446-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7056EA67-E648-4A7A-A7C1-2F37528D7354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E16B3F69-0E3C-45DF-8ECB-A3D5720E7BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8446-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,19 +1227,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q124"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +1265,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1297,7 +1304,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1340,7 +1347,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1379,7 +1386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1432,7 +1439,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1485,7 +1492,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1538,7 +1545,7 @@
         <v>-1.22</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1591,7 +1598,7 @@
         <v>-3.39</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1644,7 +1651,7 @@
         <v>-5.97</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1697,7 +1704,7 @@
         <v>-8.27</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1750,7 +1757,7 @@
         <v>-26.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1803,7 +1810,7 @@
         <v>-27.2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1856,7 +1863,7 @@
         <v>-28.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1909,7 +1916,7 @@
         <v>-29.3</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1962,7 +1969,7 @@
         <v>-29.6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2015,7 +2022,7 @@
         <v>-30.2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2068,7 +2075,7 @@
         <v>-29.4</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2121,7 +2128,7 @@
         <v>-28.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2174,7 +2181,7 @@
         <v>-28.1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2227,7 +2234,7 @@
         <v>-27.3</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2280,7 +2287,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2333,7 +2340,7 @@
         <v>-23.6</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2386,7 +2393,7 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2439,7 +2446,7 @@
         <v>-20.9</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2492,7 +2499,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2545,7 +2552,7 @@
         <v>-22.2</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2598,7 +2605,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2651,7 +2658,7 @@
         <v>-21.2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2704,7 +2711,7 @@
         <v>-21.2</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2757,7 +2764,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2810,7 +2817,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2863,7 +2870,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2916,7 +2923,7 @@
         <v>-6.84</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2969,7 +2976,7 @@
         <v>-3.42</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>-5.01</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3075,7 +3082,7 @@
         <v>-6.71</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3181,7 +3188,7 @@
         <v>-9.91</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3234,7 +3241,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3287,7 +3294,7 @@
         <v>-13.4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3340,7 +3347,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3393,7 +3400,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3446,7 +3453,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3499,7 +3506,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3552,7 +3559,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3605,7 +3612,7 @@
         <v>-2.31</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3658,7 +3665,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3711,7 +3718,7 @@
         <v>-1.88</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3764,7 +3771,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3817,7 +3824,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3923,7 +3930,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3976,7 +3983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4029,7 +4036,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4082,7 +4089,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4135,7 +4142,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4188,7 +4195,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4241,7 +4248,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4294,7 +4301,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4347,7 +4354,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4400,7 +4407,7 @@
         <v>-4.82</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4453,7 +4460,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4506,7 +4513,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4559,7 +4566,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4612,7 +4619,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4665,7 +4672,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4718,7 +4725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4771,7 +4778,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4824,7 +4831,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4877,7 +4884,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4930,7 +4937,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4983,7 +4990,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5036,7 +5043,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5089,7 +5096,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5142,7 +5149,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5195,7 +5202,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5248,7 +5255,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5301,7 +5308,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5354,7 +5361,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5407,7 +5414,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5460,7 +5467,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5513,7 +5520,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5566,7 +5573,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5619,7 +5626,7 @@
         <v>63.3</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5672,7 +5679,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5725,7 +5732,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5778,7 +5785,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5831,7 +5838,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5884,7 +5891,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5937,7 +5944,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5990,7 +5997,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6043,7 +6050,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6096,7 +6103,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6149,7 +6156,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6202,7 +6209,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6255,7 +6262,7 @@
         <v>-0.73</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6308,7 +6315,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6361,7 +6368,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6414,7 +6421,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6467,7 +6474,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6520,7 +6527,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6573,7 +6580,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6626,7 +6633,7 @@
         <v>-3.74</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6679,7 +6686,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6732,7 +6739,7 @@
         <v>-0.34</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6785,7 +6792,7 @@
         <v>-4.13</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6838,7 +6845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6891,7 +6898,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6944,7 +6951,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6997,7 +7004,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7050,7 +7057,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7103,7 +7110,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7156,7 +7163,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7209,7 +7216,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7262,7 +7269,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7315,7 +7322,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7368,7 +7375,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7421,7 +7428,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7474,7 +7481,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7527,7 +7534,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7580,7 +7587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7633,7 +7640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7686,7 +7693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7754,7 +7761,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>